--- a/outputs/evaluation/CF_M01_req_eval_llm_report.xlsx
+++ b/outputs/evaluation/CF_M01_req_eval_llm_report.xlsx
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3857</v>
+        <v>0.3877</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.3483</v>
+        <v>0.3481</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M01_req_eval_llm_report.xlsx
+++ b/outputs/evaluation/CF_M01_req_eval_llm_report.xlsx
@@ -413,196 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>LLM_ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>LLM_description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>LLM_type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>LLM_pageNumber</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>LLM_concept</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>LLM_categorization</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>LLM_relatedTo</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>LLM_fixes</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>closest_GT_ID</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>closest_GT_description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>best_similarity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>R_23</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>The platform shall scale dynamically with changes in simultaneous connections.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>R_22</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>CF_M01_R05</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>The connection status can only be connected or not connected.</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0.1564</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>R_25</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>The system shall scale automatically as data increases.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>R_24</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>CF_M01_R23</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>The system must be able to grow in capacity as the volume of data increases.</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.3877</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>R_27</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Users without permission shall not be able to access data for which they do not have permission.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>R_26</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>CF_M01_R25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Unauthorized users cannot access data they do not own.</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.3481</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>